--- a/frontend/public/demo/client-import-template.xlsx
+++ b/frontend/public/demo/client-import-template.xlsx
@@ -56,7 +56,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -64,17 +64,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
